--- a/docs/point-tags/point-tags.xlsx
+++ b/docs/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -575,6 +575,102 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>YYYY;DD/MM/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>building_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>barn;house;hotel;store;apartment;office;warehouse;garage;shed;cabin;church;school;hospital;factory;restaurant;library</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>military_installation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>military_installation_structure;fort;castle;airbase;base;camp;garrison;bunker;outpost</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>amenity</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>museum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/point-tags/point-tags.xlsx
+++ b/docs/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -671,6 +671,30 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>military_installation_structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>barracks;kitchen;mess_hall;garage;armory;watchtower;gatehouse;infirmary;stable;guardhouse</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/point-tags/point-tags.xlsx
+++ b/docs/point-tags/point-tags.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -695,6 +695,78 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>(free text — the brand's real name, spaces/punctuation as written, e.g. McDonald's or Shake Shack)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>(free text — mirrors the point's own name; rarely set directly)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>brand_historic_location</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>first;first_without_name;first_with_name;municipality;registered;unique_location</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
